--- a/data/trans_orig/Q4503_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4503_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>281791</t>
+          <t>282364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>340297</t>
+          <t>341102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158447</t>
+          <t>158260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>209796</t>
+          <t>206729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>451262</t>
+          <t>454927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>529501</t>
+          <t>529166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179320</t>
+          <t>179499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229110</t>
+          <t>228093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112687</t>
+          <t>109777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153606</t>
+          <t>154862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>302626</t>
+          <t>301180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>370766</t>
+          <t>368481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201401</t>
+          <t>205028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>254848</t>
+          <t>259455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>184613</t>
+          <t>182990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234374</t>
+          <t>235922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>398102</t>
+          <t>404190</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>475743</t>
+          <t>474585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41806</t>
+          <t>40227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68552</t>
+          <t>68530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125105</t>
+          <t>124044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169573</t>
+          <t>169228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>173694</t>
+          <t>174285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226790</t>
+          <t>230089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>208766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262355</t>
+          <t>263890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>612256</t>
+          <t>611486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>681797</t>
+          <t>685763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>836820</t>
+          <t>834284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930686</t>
+          <t>930225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211066</t>
+          <t>214242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269280</t>
+          <t>274273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119075</t>
+          <t>119899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165777</t>
+          <t>166235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>346568</t>
+          <t>344593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420253</t>
+          <t>420965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289089</t>
+          <t>288489</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>349242</t>
+          <t>351973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145010</t>
+          <t>145740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>193106</t>
+          <t>191105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>443784</t>
+          <t>441682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>527710</t>
+          <t>525001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>526010</t>
+          <t>529672</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>604857</t>
+          <t>604835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>454604</t>
+          <t>455740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>532990</t>
+          <t>529222</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1006612</t>
+          <t>1005223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1114323</t>
+          <t>1112367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158843</t>
+          <t>156559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209518</t>
+          <t>209050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194402</t>
+          <t>194259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250715</t>
+          <t>249909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>367287</t>
+          <t>367195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446570</t>
+          <t>445320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349577</t>
+          <t>351928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>419956</t>
+          <t>421988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>521876</t>
+          <t>521754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>597398</t>
+          <t>601481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>895630</t>
+          <t>896158</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>997676</t>
+          <t>998395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65072</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99683</t>
+          <t>100387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45095</t>
+          <t>46291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>76646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117625</t>
+          <t>117257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165622</t>
+          <t>166112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82113</t>
+          <t>78292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119008</t>
+          <t>116465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89786</t>
+          <t>89765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148014</t>
+          <t>149178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196262</t>
+          <t>197778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>149768</t>
+          <t>149305</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193302</t>
+          <t>193804</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>116150</t>
+          <t>118179</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>159303</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>279293</t>
+          <t>278768</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338446</t>
+          <t>336362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57572</t>
+          <t>57682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91589</t>
+          <t>92605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,49 +2450,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>63395</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>49375</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>79130</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>16,61%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>63395</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>48422</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>79261</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>132</t>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114741</t>
+          <t>114956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162695</t>
+          <t>160614</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107842</t>
+          <t>107224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150128</t>
+          <t>148056</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125212</t>
+          <t>124420</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164658</t>
+          <t>162909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245323</t>
+          <t>245722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>301985</t>
+          <t>303363</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>590150</t>
+          <t>587166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>679792</t>
+          <t>678947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>342352</t>
+          <t>345318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>416815</t>
+          <t>422395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>956130</t>
+          <t>958724</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1077521</t>
+          <t>1076422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>572498</t>
+          <t>576535</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>664729</t>
+          <t>666059</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>335225</t>
+          <t>331692</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>409389</t>
+          <t>407869</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>930941</t>
+          <t>931155</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1041380</t>
+          <t>1046958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>910774</t>
+          <t>916478</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1021040</t>
+          <t>1020974</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>791715</t>
+          <t>790991</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>891243</t>
+          <t>894595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1733942</t>
+          <t>1726403</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1885133</t>
+          <t>1878397</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>277017</t>
+          <t>276381</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>345586</t>
+          <t>345664</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>390914</t>
+          <t>390174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>467706</t>
+          <t>469805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>685311</t>
+          <t>688680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>790906</t>
+          <t>789107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>695778</t>
+          <t>695882</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>792127</t>
+          <t>793791</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1299252</t>
+          <t>1294751</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1410337</t>
+          <t>1414433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2033405</t>
+          <t>2024117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2187074</t>
+          <t>2181251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>320853</t>
+          <t>321801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382587</t>
+          <t>382818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>213312</t>
+          <t>213680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>274541</t>
+          <t>269741</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>550603</t>
+          <t>551527</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>638590</t>
+          <t>638660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127039</t>
+          <t>126426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172459</t>
+          <t>172632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158156</t>
+          <t>159029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210242</t>
+          <t>209668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>300587</t>
+          <t>298640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>369261</t>
+          <t>365667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>111635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155802</t>
+          <t>156505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>177540</t>
+          <t>178185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>232798</t>
+          <t>231052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>301263</t>
+          <t>301654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>373626</t>
+          <t>378857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>51352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70967</t>
+          <t>72087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108482</t>
+          <t>109480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106680</t>
+          <t>105819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149082</t>
+          <t>150679</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277164</t>
+          <t>275272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335911</t>
+          <t>336965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>582978</t>
+          <t>582667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>653665</t>
+          <t>655430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870711</t>
+          <t>877684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970561</t>
+          <t>973520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389881</t>
+          <t>381525</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>460449</t>
+          <t>457808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210606</t>
+          <t>206958</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269648</t>
+          <t>265607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>616618</t>
+          <t>616136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>709143</t>
+          <t>711403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376573</t>
+          <t>375921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453190</t>
+          <t>453363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224140</t>
+          <t>226312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288850</t>
+          <t>287765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619830</t>
+          <t>624584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>715164</t>
+          <t>720721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>379692</t>
+          <t>383337</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>453151</t>
+          <t>458390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>345328</t>
+          <t>346766</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>411054</t>
+          <t>415874</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>743614</t>
+          <t>742607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>847695</t>
+          <t>847008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88966</t>
+          <t>91160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131225</t>
+          <t>130975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159730</t>
+          <t>157474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213569</t>
+          <t>209442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>260633</t>
+          <t>260896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>328640</t>
+          <t>330731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>551824</t>
+          <t>552861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635093</t>
+          <t>638034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654771</t>
+          <t>657742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737382</t>
+          <t>740533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1234307</t>
+          <t>1228301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1349731</t>
+          <t>1350102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>65635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101644</t>
+          <t>99778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89805</t>
+          <t>87663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128784</t>
+          <t>127310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177853</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81856</t>
+          <t>81918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>120497</t>
+          <t>122023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66248</t>
+          <t>64399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101034</t>
+          <t>101334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>157541</t>
+          <t>156189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208735</t>
+          <t>208384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114441</t>
+          <t>113445</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156486</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88899</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125354</t>
+          <t>124174</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>213522</t>
+          <t>214972</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>267743</t>
+          <t>269817</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>48260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42281</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72279</t>
+          <t>72588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73630</t>
+          <t>72862</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109884</t>
+          <t>110080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109841</t>
+          <t>110345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151242</t>
+          <t>151142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120634</t>
+          <t>118576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>161866</t>
+          <t>160048</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241136</t>
+          <t>243684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302471</t>
+          <t>301332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>803017</t>
+          <t>802715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>906084</t>
+          <t>911654</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>504170</t>
+          <t>507671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>593202</t>
+          <t>595070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1337535</t>
+          <t>1328715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1476750</t>
+          <t>1476909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>613440</t>
+          <t>613529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>708071</t>
+          <t>715437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>480469</t>
+          <t>480355</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>567056</t>
+          <t>564161</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1123969</t>
+          <t>1120474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1250315</t>
+          <t>1245920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>639012</t>
+          <t>636326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>737194</t>
+          <t>734949</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>641758</t>
+          <t>642418</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>733262</t>
+          <t>739569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,47 +6013,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1370858</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1300372</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1440134</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>20,71%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1370858</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1305012</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1436593</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156523</t>
+          <t>155473</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207460</t>
+          <t>209620</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>293007</t>
+          <t>295009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>364880</t>
+          <t>365224</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>463763</t>
+          <t>465156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>552656</t>
+          <t>554707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>973107</t>
+          <t>975262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1084969</t>
+          <t>1089660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1398042</t>
+          <t>1402982</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1521886</t>
+          <t>1520120</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2406180</t>
+          <t>2403235</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2570451</t>
+          <t>2572723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119923</t>
+          <t>120153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162068</t>
+          <t>160740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102717</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148194</t>
+          <t>149428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236897</t>
+          <t>236117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>296830</t>
+          <t>298192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181695</t>
+          <t>181022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228105</t>
+          <t>227604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171771</t>
+          <t>171347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>225878</t>
+          <t>224723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>365097</t>
+          <t>364952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435702</t>
+          <t>436105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125918</t>
+          <t>129127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>171351</t>
+          <t>171016</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131078</t>
+          <t>132207</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176778</t>
+          <t>179014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>271007</t>
+          <t>271343</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>334005</t>
+          <t>338383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>47207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79576</t>
+          <t>79832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84387</t>
+          <t>83367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123620</t>
+          <t>123840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195949</t>
+          <t>195936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242200</t>
+          <t>245286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422691</t>
+          <t>420946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485714</t>
+          <t>484022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>634015</t>
+          <t>630114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715791</t>
+          <t>714360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>293277</t>
+          <t>293953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>361692</t>
+          <t>359588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193845</t>
+          <t>195518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253100</t>
+          <t>254352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502996</t>
+          <t>504880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>591659</t>
+          <t>592583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507460</t>
+          <t>502098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>588192</t>
+          <t>586160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455425</t>
+          <t>454033</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532815</t>
+          <t>528261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>983416</t>
+          <t>979910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1101078</t>
+          <t>1092813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>471454</t>
+          <t>470628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>548599</t>
+          <t>552128</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>443548</t>
+          <t>442018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>517649</t>
+          <t>519908</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>937783</t>
+          <t>939767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1050589</t>
+          <t>1050499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151166</t>
+          <t>151213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201858</t>
+          <t>202985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156485</t>
+          <t>160506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208975</t>
+          <t>210283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320570</t>
+          <t>327167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394182</t>
+          <t>397248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>469784</t>
+          <t>471246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546927</t>
+          <t>551898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>561990</t>
+          <t>562684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642288</t>
+          <t>644773</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1051900</t>
+          <t>1056518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168310</t>
+          <t>1166768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80162</t>
+          <t>80931</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119426</t>
+          <t>117213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73005</t>
+          <t>73289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109969</t>
+          <t>109444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165978</t>
+          <t>165073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216711</t>
+          <t>216001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143277</t>
+          <t>143781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186774</t>
+          <t>188058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115790</t>
+          <t>117046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157911</t>
+          <t>158870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272614</t>
+          <t>270870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330634</t>
+          <t>332581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108763</t>
+          <t>107482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150243</t>
+          <t>148038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113781</t>
+          <t>113855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154492</t>
+          <t>156013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>234094</t>
+          <t>234667</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>292360</t>
+          <t>291447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28781</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>57343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72100</t>
+          <t>71061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79334</t>
+          <t>77339</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116855</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95313</t>
+          <t>95848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134586</t>
+          <t>135612</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111910</t>
+          <t>113173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153133</t>
+          <t>153624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216141</t>
+          <t>217138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272039</t>
+          <t>273652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>519671</t>
+          <t>515455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>608569</t>
+          <t>602484</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>401894</t>
+          <t>400373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>483169</t>
+          <t>482591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>946671</t>
+          <t>947110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1072497</t>
+          <t>1066801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>864314</t>
+          <t>861781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>967470</t>
+          <t>965592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>778479</t>
+          <t>774082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>880195</t>
+          <t>878182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1667291</t>
+          <t>1664567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1819379</t>
+          <t>1815509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>738521</t>
+          <t>739185</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>841056</t>
+          <t>835518</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>718460</t>
+          <t>720295</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>817951</t>
+          <t>818205</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1491872</t>
+          <t>1493083</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1632353</t>
+          <t>1624896</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>225970</t>
+          <t>224658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>289605</t>
+          <t>285598</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>268203</t>
+          <t>273077</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>338917</t>
+          <t>338466</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>513234</t>
+          <t>514030</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>603484</t>
+          <t>603325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>785685</t>
+          <t>789851</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>888206</t>
+          <t>888637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1131513</t>
+          <t>1131086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1242648</t>
+          <t>1247012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1954562</t>
+          <t>1951346</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2104940</t>
+          <t>2108168</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4503_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4503_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282364</t>
+          <t>283196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>341102</t>
+          <t>341322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158260</t>
+          <t>159155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>206729</t>
+          <t>208503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>454927</t>
+          <t>451275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>529166</t>
+          <t>531977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179499</t>
+          <t>179409</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228093</t>
+          <t>230758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109777</t>
+          <t>110753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>154844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301180</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>368481</t>
+          <t>371123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>205028</t>
+          <t>204138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259455</t>
+          <t>256390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>182990</t>
+          <t>184913</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>235922</t>
+          <t>237139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>404190</t>
+          <t>401135</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>474585</t>
+          <t>474579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40227</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68530</t>
+          <t>69488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124044</t>
+          <t>123872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169228</t>
+          <t>170627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174285</t>
+          <t>175423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>230089</t>
+          <t>227860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208766</t>
+          <t>206392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263890</t>
+          <t>259758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>611486</t>
+          <t>611749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>685763</t>
+          <t>683958</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>834284</t>
+          <t>832572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930225</t>
+          <t>926978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214242</t>
+          <t>213414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274273</t>
+          <t>271778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119899</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166235</t>
+          <t>165770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,47 +1464,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>382106</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>343869</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>423078</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>382106</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>344593</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>420965</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288489</t>
+          <t>289968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>351973</t>
+          <t>353928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145740</t>
+          <t>143313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191105</t>
+          <t>194423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>441682</t>
+          <t>443751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>525001</t>
+          <t>523856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>529672</t>
+          <t>522986</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>604835</t>
+          <t>601793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>455740</t>
+          <t>456586</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>529222</t>
+          <t>531831</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1005223</t>
+          <t>1000172</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1112367</t>
+          <t>1115982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156559</t>
+          <t>159085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209050</t>
+          <t>209007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194259</t>
+          <t>193266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249909</t>
+          <t>248636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>367195</t>
+          <t>367657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>445320</t>
+          <t>439353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351928</t>
+          <t>349894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>421988</t>
+          <t>419643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>521754</t>
+          <t>524016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601481</t>
+          <t>599560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>896158</t>
+          <t>890044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>998395</t>
+          <t>998555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65675</t>
+          <t>64988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100387</t>
+          <t>98666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46291</t>
+          <t>46042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76646</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117257</t>
+          <t>117783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166112</t>
+          <t>163821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>80521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116465</t>
+          <t>116050</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>57862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89765</t>
+          <t>91722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149178</t>
+          <t>145883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197778</t>
+          <t>193889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>149305</t>
+          <t>149689</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193804</t>
+          <t>193087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118179</t>
+          <t>117554</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159303</t>
+          <t>156237</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>278768</t>
+          <t>278800</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336362</t>
+          <t>337408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>59002</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92605</t>
+          <t>92004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49375</t>
+          <t>49151</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79130</t>
+          <t>79863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114956</t>
+          <t>115678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160614</t>
+          <t>159073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107224</t>
+          <t>107228</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148056</t>
+          <t>147686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124420</t>
+          <t>125095</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>162909</t>
+          <t>165761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245722</t>
+          <t>245454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>303363</t>
+          <t>302056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>587166</t>
+          <t>588684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>678947</t>
+          <t>675709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>345318</t>
+          <t>346624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>422395</t>
+          <t>417455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>958724</t>
+          <t>956166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1076422</t>
+          <t>1075938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576535</t>
+          <t>573835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>666059</t>
+          <t>668001</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>331692</t>
+          <t>331289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>407869</t>
+          <t>407646</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>931155</t>
+          <t>933224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1046958</t>
+          <t>1048667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>916478</t>
+          <t>914554</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1020974</t>
+          <t>1013970</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>790991</t>
+          <t>790445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>894595</t>
+          <t>890238</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1726403</t>
+          <t>1737556</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1878397</t>
+          <t>1878170</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>276381</t>
+          <t>278118</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>345664</t>
+          <t>349244</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>390174</t>
+          <t>391435</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>469805</t>
+          <t>470762</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>688680</t>
+          <t>687227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>789107</t>
+          <t>790801</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>695882</t>
+          <t>702031</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>793791</t>
+          <t>794746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1294751</t>
+          <t>1291248</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1414433</t>
+          <t>1416183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2024117</t>
+          <t>2026825</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2181251</t>
+          <t>2178731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>321801</t>
+          <t>320316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382818</t>
+          <t>379880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>213680</t>
+          <t>213344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269741</t>
+          <t>271128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>551527</t>
+          <t>552550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>638660</t>
+          <t>638452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126426</t>
+          <t>124775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172632</t>
+          <t>172242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159029</t>
+          <t>157711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209668</t>
+          <t>208046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>298640</t>
+          <t>297884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>365667</t>
+          <t>368221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111635</t>
+          <t>111995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156505</t>
+          <t>155172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>178185</t>
+          <t>177921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>231052</t>
+          <t>233140</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>301654</t>
+          <t>300971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>378857</t>
+          <t>373347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51352</t>
+          <t>50907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72087</t>
+          <t>73275</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109480</t>
+          <t>111393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105819</t>
+          <t>104890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150679</t>
+          <t>150018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275272</t>
+          <t>275410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>336965</t>
+          <t>333927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>582667</t>
+          <t>587977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>655430</t>
+          <t>660321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877684</t>
+          <t>874690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973520</t>
+          <t>969455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>381525</t>
+          <t>387870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>457808</t>
+          <t>461638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206958</t>
+          <t>212668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>265607</t>
+          <t>270827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>616136</t>
+          <t>617324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>711403</t>
+          <t>711223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375921</t>
+          <t>375911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453363</t>
+          <t>453011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226312</t>
+          <t>228419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287765</t>
+          <t>287280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624584</t>
+          <t>625449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>720721</t>
+          <t>719795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>383337</t>
+          <t>382039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>458390</t>
+          <t>461411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>346766</t>
+          <t>344669</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>415874</t>
+          <t>411260</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>742607</t>
+          <t>740283</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>847008</t>
+          <t>842275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91160</t>
+          <t>89040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130975</t>
+          <t>130738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157474</t>
+          <t>158455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209442</t>
+          <t>213685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>260896</t>
+          <t>259747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330731</t>
+          <t>324526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>552861</t>
+          <t>550795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638034</t>
+          <t>639732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657742</t>
+          <t>654481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>740533</t>
+          <t>739758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1228301</t>
+          <t>1227686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1350102</t>
+          <t>1351996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65635</t>
+          <t>64269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99778</t>
+          <t>100686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53315</t>
+          <t>56020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87663</t>
+          <t>91883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127310</t>
+          <t>130175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176116</t>
+          <t>178736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81918</t>
+          <t>83987</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122023</t>
+          <t>120409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64399</t>
+          <t>64666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101334</t>
+          <t>98997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156189</t>
+          <t>156604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208384</t>
+          <t>205117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113445</t>
+          <t>111831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154059</t>
+          <t>154044</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87766</t>
+          <t>85872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124174</t>
+          <t>124427</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>214972</t>
+          <t>210731</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269817</t>
+          <t>267311</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48260</t>
+          <t>46651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42626</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72588</t>
+          <t>72669</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72862</t>
+          <t>71601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110080</t>
+          <t>109336</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110345</t>
+          <t>110213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151142</t>
+          <t>152756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>118576</t>
+          <t>120950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>160048</t>
+          <t>163179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>243684</t>
+          <t>243368</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>301332</t>
+          <t>302510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>802715</t>
+          <t>806034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>911654</t>
+          <t>910022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>507671</t>
+          <t>510569</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>595070</t>
+          <t>600763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1328715</t>
+          <t>1334847</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1476909</t>
+          <t>1471699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>613529</t>
+          <t>617914</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>715437</t>
+          <t>707675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>480355</t>
+          <t>477302</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>564161</t>
+          <t>562665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1120474</t>
+          <t>1120498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1245920</t>
+          <t>1252358</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>636326</t>
+          <t>638146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>734949</t>
+          <t>734132</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>642418</t>
+          <t>640808</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>739569</t>
+          <t>735433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1300372</t>
+          <t>1305894</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1440134</t>
+          <t>1439428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>155473</t>
+          <t>152738</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209620</t>
+          <t>207609</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>295009</t>
+          <t>297548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>365224</t>
+          <t>367306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>465156</t>
+          <t>462871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>554707</t>
+          <t>554351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>975262</t>
+          <t>975462</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1089660</t>
+          <t>1085878</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1402982</t>
+          <t>1394211</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1520120</t>
+          <t>1517913</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2403235</t>
+          <t>2408906</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2572723</t>
+          <t>2571843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120153</t>
+          <t>119818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160740</t>
+          <t>159650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106225</t>
+          <t>105252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149428</t>
+          <t>148291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236117</t>
+          <t>238250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>298192</t>
+          <t>295217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181022</t>
+          <t>180525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227604</t>
+          <t>228229</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171347</t>
+          <t>172177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224723</t>
+          <t>223645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>364952</t>
+          <t>364301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436105</t>
+          <t>434958</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129127</t>
+          <t>127209</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>171016</t>
+          <t>170421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132207</t>
+          <t>130856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179014</t>
+          <t>179478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>271343</t>
+          <t>271683</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>338383</t>
+          <t>336420</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>53784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47207</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79832</t>
+          <t>80549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83367</t>
+          <t>82799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123840</t>
+          <t>123754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195936</t>
+          <t>197690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245286</t>
+          <t>246807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>420946</t>
+          <t>418793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484022</t>
+          <t>485689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>630114</t>
+          <t>630298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714360</t>
+          <t>713403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>293953</t>
+          <t>289711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359588</t>
+          <t>363238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195518</t>
+          <t>194869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254352</t>
+          <t>253022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>504880</t>
+          <t>508642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>592583</t>
+          <t>597753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502098</t>
+          <t>506022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586160</t>
+          <t>586955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454033</t>
+          <t>456880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>528261</t>
+          <t>532374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>979910</t>
+          <t>988065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092813</t>
+          <t>1097152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>470628</t>
+          <t>472485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>552128</t>
+          <t>554179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>442018</t>
+          <t>441024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>519908</t>
+          <t>518684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>939767</t>
+          <t>930573</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1050499</t>
+          <t>1048219</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151213</t>
+          <t>149380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202985</t>
+          <t>201716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160506</t>
+          <t>158835</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210283</t>
+          <t>208376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327167</t>
+          <t>322018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397248</t>
+          <t>394447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>471246</t>
+          <t>467386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551898</t>
+          <t>547007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>562684</t>
+          <t>559301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644773</t>
+          <t>645348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1056518</t>
+          <t>1047112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1166768</t>
+          <t>1165104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>81084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117213</t>
+          <t>119233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,82 +8029,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>91048</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>73490</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>109619</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>189644</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>162478</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>215367</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>17,33%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>14,85%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>91048</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>73289</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>109444</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>189644</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>165073</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>216001</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>17,33%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143781</t>
+          <t>145636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>188846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117046</t>
+          <t>113555</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158870</t>
+          <t>156194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270870</t>
+          <t>273002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>332581</t>
+          <t>333789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107482</t>
+          <t>106992</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148038</t>
+          <t>148075</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113855</t>
+          <t>114459</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>156013</t>
+          <t>157151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>234667</t>
+          <t>235320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>291447</t>
+          <t>290383</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29718</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57343</t>
+          <t>55782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>42251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71061</t>
+          <t>73002</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77339</t>
+          <t>78398</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>117061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95848</t>
+          <t>93523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135612</t>
+          <t>131770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113173</t>
+          <t>110782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153624</t>
+          <t>151305</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>217138</t>
+          <t>217947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273652</t>
+          <t>273088</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>515455</t>
+          <t>520898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>602484</t>
+          <t>608410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>400373</t>
+          <t>400710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>482591</t>
+          <t>483248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,47 +8746,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1004858</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>943237</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1063451</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>13,7%</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1004858</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>947110</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1066801</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>14,6%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>861781</t>
+          <t>864608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>965592</t>
+          <t>970364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>774082</t>
+          <t>770355</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>878182</t>
+          <t>868746</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1664567</t>
+          <t>1669064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1815509</t>
+          <t>1811434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>739185</t>
+          <t>742807</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>835518</t>
+          <t>838691</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>720295</t>
+          <t>721012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>818205</t>
+          <t>821288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1493083</t>
+          <t>1492091</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1624896</t>
+          <t>1628864</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>224658</t>
+          <t>223859</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>285598</t>
+          <t>286677</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>273077</t>
+          <t>270335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>338466</t>
+          <t>338133</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>514030</t>
+          <t>507471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>603325</t>
+          <t>600765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>789851</t>
+          <t>789278</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>888637</t>
+          <t>895230</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1131086</t>
+          <t>1130047</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1247012</t>
+          <t>1245744</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1951346</t>
+          <t>1952499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2108168</t>
+          <t>2103921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
